--- a/static/data/exports/Retro_TR_GE_2019.xlsx
+++ b/static/data/exports/Retro_TR_GE_2019.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/static/data/exports/Retro_TR_GE_2019.xlsx
+++ b/static/data/exports/Retro_TR_GE_2019.xlsx
@@ -726,11 +726,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E5" t="n">
         <v>4787</v>
@@ -1532,11 +1532,11 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E18" t="n">
         <v>4211</v>
@@ -2400,11 +2400,11 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E32" t="n">
         <v>7623</v>
@@ -3268,11 +3268,11 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E46" t="n">
         <v>6756</v>
@@ -4136,11 +4136,11 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E60" t="n">
         <v>4384</v>
@@ -5004,11 +5004,11 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E74" t="n">
         <v>9355</v>
@@ -5872,11 +5872,11 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E88" t="n">
         <v>6055</v>
@@ -6297,20 +6297,20 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>1781589</v>
+        <v>1781590</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Arun Kumar Bhaumik</t>
+          <t>Prabir Debnath</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>SUCI(C)</t>
+          <t>AMB</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>22925</v>
+        <v>22929</v>
       </c>
       <c r="E95" t="n">
         <v>64</v>
@@ -6334,12 +6334,12 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>Arun Kumar Bhaumik</t>
+          <t>Prabir Debnath</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>SUCI(C)</t>
+          <t>AMB</t>
         </is>
       </c>
       <c r="Q95" t="b">
@@ -6359,20 +6359,20 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>1781590</v>
+        <v>1781589</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Prabir Debnath</t>
+          <t>Arun Kumar Bhaumik</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>AMB</t>
+          <t>SUCI(C)</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>22929</v>
+        <v>22925</v>
       </c>
       <c r="E96" t="n">
         <v>64</v>
@@ -6396,12 +6396,12 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Prabir Debnath</t>
+          <t>Arun Kumar Bhaumik</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>AMB</t>
+          <t>SUCI(C)</t>
         </is>
       </c>
       <c r="Q96" t="b">
@@ -6740,11 +6740,11 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E102" t="n">
         <v>6785</v>
@@ -7608,11 +7608,11 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E116" t="n">
         <v>6091</v>
@@ -8476,11 +8476,11 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E130" t="n">
         <v>5115</v>
@@ -9406,11 +9406,11 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E145" t="n">
         <v>4560</v>
@@ -10212,11 +10212,11 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E158" t="n">
         <v>3072</v>
@@ -11018,11 +11018,11 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E171" t="n">
         <v>10196</v>
@@ -11886,11 +11886,11 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E185" t="n">
         <v>9733</v>
@@ -12816,11 +12816,11 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E200" t="n">
         <v>5009</v>
@@ -13684,11 +13684,11 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E214" t="n">
         <v>2929</v>
@@ -14614,11 +14614,11 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E229" t="n">
         <v>3888</v>
@@ -15358,11 +15358,11 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E241" t="n">
         <v>7177</v>
@@ -16350,11 +16350,11 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D257" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E257" t="n">
         <v>1666</v>
@@ -17156,11 +17156,11 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D270" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E270" t="n">
         <v>3908</v>
@@ -18024,11 +18024,11 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D284" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E284" t="n">
         <v>5459</v>
@@ -18892,11 +18892,11 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D298" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E298" t="n">
         <v>4063</v>
@@ -19760,11 +19760,11 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D312" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E312" t="n">
         <v>4687</v>
@@ -20690,11 +20690,11 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D327" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E327" t="n">
         <v>2784</v>
@@ -21310,11 +21310,11 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D337" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E337" t="n">
         <v>6636</v>
@@ -22054,11 +22054,11 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D349" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E349" t="n">
         <v>2874</v>
@@ -22674,11 +22674,11 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D359" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E359" t="n">
         <v>3776</v>
@@ -23356,11 +23356,11 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D370" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E370" t="n">
         <v>5207</v>
@@ -24038,11 +24038,11 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D381" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E381" t="n">
         <v>4568</v>
@@ -24720,11 +24720,11 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D392" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E392" t="n">
         <v>6166</v>
@@ -25588,11 +25588,11 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D406" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E406" t="n">
         <v>5427</v>
@@ -26456,11 +26456,11 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D420" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E420" t="n">
         <v>5558</v>
@@ -27324,11 +27324,11 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D434" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E434" t="n">
         <v>5056</v>
@@ -28130,11 +28130,11 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D447" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E447" t="n">
         <v>7354</v>
@@ -28998,11 +28998,11 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D461" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E461" t="n">
         <v>7556</v>
@@ -29928,11 +29928,11 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D476" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E476" t="n">
         <v>6549</v>
@@ -30734,11 +30734,11 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D489" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E489" t="n">
         <v>9547</v>
@@ -31416,11 +31416,11 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D500" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E500" t="n">
         <v>8126</v>
@@ -31655,11 +31655,11 @@
     </row>
     <row r="504">
       <c r="A504" t="n">
-        <v>1781998</v>
+        <v>1781999</v>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Bijoy Debbarma</t>
+          <t>Subir Kumar Jamatia</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
@@ -31692,7 +31692,7 @@
       </c>
       <c r="K504" t="inlineStr">
         <is>
-          <t>Bijoy Debbarma</t>
+          <t>Subir Kumar Jamatia</t>
         </is>
       </c>
       <c r="L504" t="inlineStr">
@@ -31717,11 +31717,11 @@
     </row>
     <row r="505">
       <c r="A505" t="n">
-        <v>1781999</v>
+        <v>1781998</v>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Subir Kumar Jamatia</t>
+          <t>Bijoy Debbarma</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -31754,7 +31754,7 @@
       </c>
       <c r="K505" t="inlineStr">
         <is>
-          <t>Subir Kumar Jamatia</t>
+          <t>Bijoy Debbarma</t>
         </is>
       </c>
       <c r="L505" t="inlineStr">
@@ -32098,11 +32098,11 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D511" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E511" t="n">
         <v>11458</v>
@@ -32780,11 +32780,11 @@
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D522" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E522" t="n">
         <v>10744</v>
@@ -33586,11 +33586,11 @@
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D535" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E535" t="n">
         <v>3861</v>
@@ -34206,11 +34206,11 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D545" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E545" t="n">
         <v>5351</v>
@@ -34826,11 +34826,11 @@
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D555" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E555" t="n">
         <v>7529</v>
@@ -35570,11 +35570,11 @@
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D567" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E567" t="n">
         <v>7035</v>
@@ -35809,20 +35809,20 @@
     </row>
     <row r="571">
       <c r="A571" t="n">
-        <v>1782065</v>
+        <v>1782066</v>
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>Chitta Ranjan Debbarma</t>
+          <t>Karnadhan Chakma</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>AMB</t>
         </is>
       </c>
       <c r="D571" t="n">
-        <v>22919</v>
+        <v>22929</v>
       </c>
       <c r="E571" t="n">
         <v>199</v>
@@ -35846,12 +35846,12 @@
       </c>
       <c r="K571" t="inlineStr">
         <is>
-          <t>Chitta Ranjan Debbarma</t>
+          <t>Karnadhan Chakma</t>
         </is>
       </c>
       <c r="L571" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>AMB</t>
         </is>
       </c>
       <c r="Q571" t="b">
@@ -35871,20 +35871,20 @@
     </row>
     <row r="572">
       <c r="A572" t="n">
-        <v>1782066</v>
+        <v>1782065</v>
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>Karnadhan Chakma</t>
+          <t>Chitta Ranjan Debbarma</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>AMB</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D572" t="n">
-        <v>22929</v>
+        <v>22919</v>
       </c>
       <c r="E572" t="n">
         <v>199</v>
@@ -35908,12 +35908,12 @@
       </c>
       <c r="K572" t="inlineStr">
         <is>
-          <t>Karnadhan Chakma</t>
+          <t>Chitta Ranjan Debbarma</t>
         </is>
       </c>
       <c r="L572" t="inlineStr">
         <is>
-          <t>AMB</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="Q572" t="b">
@@ -36252,11 +36252,11 @@
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D578" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E578" t="n">
         <v>5399</v>
@@ -36934,11 +36934,11 @@
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D589" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E589" t="n">
         <v>6030</v>
@@ -37616,11 +37616,11 @@
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D600" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E600" t="n">
         <v>8339</v>
@@ -38298,11 +38298,11 @@
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D611" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E611" t="n">
         <v>5722</v>
@@ -38980,11 +38980,11 @@
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D622" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E622" t="n">
         <v>5858</v>
@@ -39662,11 +39662,11 @@
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D633" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E633" t="n">
         <v>7678</v>
@@ -40344,11 +40344,11 @@
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D644" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E644" t="n">
         <v>5618</v>
@@ -41026,11 +41026,11 @@
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D655" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E655" t="n">
         <v>6636</v>
@@ -41708,11 +41708,11 @@
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D666" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E666" t="n">
         <v>7125</v>
@@ -42390,11 +42390,11 @@
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D677" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E677" t="n">
         <v>8125</v>
@@ -43010,11 +43010,11 @@
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D687" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E687" t="n">
         <v>7624</v>
@@ -43692,11 +43692,11 @@
       </c>
       <c r="C698" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D698" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E698" t="n">
         <v>6022</v>
@@ -44374,11 +44374,11 @@
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D709" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E709" t="n">
         <v>6601</v>
@@ -45056,11 +45056,11 @@
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D720" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E720" t="n">
         <v>7225</v>
@@ -45738,11 +45738,11 @@
       </c>
       <c r="C731" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D731" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E731" t="n">
         <v>7814</v>
@@ -46420,11 +46420,11 @@
       </c>
       <c r="C742" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D742" t="n">
-        <v>22924</v>
+        <v>22922</v>
       </c>
       <c r="E742" t="n">
         <v>9185</v>
